--- a/ig/DM_FINESS_New/ValueSet-jdv-j295-document-informatif-finess.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-jdv-j295-document-informatif-finess.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="32">
   <si>
     <t>Property</t>
   </si>
@@ -94,9 +94,6 @@
   </si>
   <si>
     <t>Operation</t>
-  </si>
-  <si>
-    <t>informatif</t>
   </si>
   <si>
     <t>=</t>
@@ -387,29 +384,29 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
+        <v>9</v>
+      </c>
+      <c r="B2" t="s" s="2">
         <v>27</v>
       </c>
-      <c r="B2" t="s" s="2">
+      <c r="C2" t="s" s="2">
         <v>28</v>
-      </c>
-      <c r="C2" t="s" s="2">
-        <v>29</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="B4" t="s" s="2">
         <v>31</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>32</v>
       </c>
     </row>
   </sheetData>

--- a/ig/DM_FINESS_New/ValueSet-jdv-j295-document-informatif-finess.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-jdv-j295-document-informatif-finess.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="33">
   <si>
     <t>Property</t>
   </si>
@@ -94,6 +94,9 @@
   </si>
   <si>
     <t>Operation</t>
+  </si>
+  <si>
+    <t>BDocumentInformatifFiness</t>
   </si>
   <si>
     <t>=</t>
@@ -384,29 +387,29 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>

--- a/ig/DM_FINESS_New/ValueSet-jdv-j295-document-informatif-finess.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-jdv-j295-document-informatif-finess.xlsx
@@ -96,7 +96,7 @@
     <t>Operation</t>
   </si>
   <si>
-    <t>BDocumentInformatifFiness</t>
+    <t>DocumentInformatifFiness</t>
   </si>
   <si>
     <t>=</t>

--- a/ig/DM_FINESS_New/ValueSet-jdv-j295-document-informatif-finess.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-jdv-j295-document-informatif-finess.xlsx
@@ -96,7 +96,7 @@
     <t>Operation</t>
   </si>
   <si>
-    <t>DocumentInformatifFiness</t>
+    <t>documentInformatifFiness</t>
   </si>
   <si>
     <t>=</t>

--- a/ig/DM_FINESS_New/ValueSet-jdv-j295-document-informatif-finess.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-jdv-j295-document-informatif-finess.xlsx
@@ -111,7 +111,7 @@
     <t>System URI</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/CodeSystem/tre-r364-type-document-administratif</t>
+    <t>https://smt.esante.gouv.fr/fhir/CodeSystem/tre-r364-type-document-structure</t>
   </si>
 </sst>
 </file>

--- a/ig/DM_FINESS_New/ValueSet-jdv-j295-document-informatif-finess.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-jdv-j295-document-informatif-finess.xlsx
@@ -111,7 +111,7 @@
     <t>System URI</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/CodeSystem/tre-r364-type-document-structure</t>
+    <t>https://smt.esante.gouv.fr/fhir/CodeSystem/tre-r364-type-document-administratif</t>
   </si>
 </sst>
 </file>
